--- a/artfynd/A 21228-2026 artfynd.xlsx
+++ b/artfynd/A 21228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114949703</v>
+        <v>114949706</v>
       </c>
       <c r="B2" t="n">
-        <v>58078</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,26 +710,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blommelund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528377</v>
+        <v>528364</v>
       </c>
       <c r="R2" t="n">
-        <v>6484387</v>
+        <v>6484404</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -773,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +773,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -805,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114950081</v>
+        <v>114950077</v>
       </c>
       <c r="B3" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,11 +823,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -854,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528405</v>
+        <v>528315</v>
       </c>
       <c r="R3" t="n">
-        <v>6484360</v>
+        <v>6484286</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -884,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-06-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +900,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -930,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114950077</v>
+        <v>114950081</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,7 +939,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -975,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528315</v>
+        <v>528405</v>
       </c>
       <c r="R4" t="n">
-        <v>6484286</v>
+        <v>6484360</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1005,22 +985,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-15</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1020,495 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114950093</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528335</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6484404</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:58</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114950076</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>528181</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6484332</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>04:54</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>04:54</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114949711</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>528185</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6484305</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
           <t>Jake Bull</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114949703</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blommelund, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>528377</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6484387</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>

--- a/artfynd/A 21228-2026 artfynd.xlsx
+++ b/artfynd/A 21228-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114949706</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950077</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950081</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114950076</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1386,6 +1416,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114949711</t>
         </is>
       </c>
     </row>
@@ -1513,8 +1548,22 @@
           <t>Rejlers - NVI Ljungsbro-Linköping</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114949703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>